--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:46</t>
+    <t xml:space="preserve">2026-09-09 20:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:51</t>
+    <t xml:space="preserve">2026-09-18 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -995,7 +995,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1004,12 +1004,12 @@
         <v>27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>27.17</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1018,12 +1018,12 @@
         <v>28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>67.63</v>
+        <v>63.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1032,12 +1032,12 @@
         <v>29</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>95.33</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1046,12 +1046,12 @@
         <v>27</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>25.61</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1060,12 +1060,12 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>63.23</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -1074,7 +1074,7 @@
         <v>29</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>92.86</v>
+        <v>95.33</v>
       </c>
     </row>
     <row r="8">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
@@ -1130,12 +1130,12 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>95.02</v>
+        <v>93.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -1144,12 +1144,12 @@
         <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>97.86</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -1158,12 +1158,12 @@
         <v>30</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>93.64</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -1172,7 +1172,7 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>94.86</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="15">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -1214,12 +1214,12 @@
         <v>32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>92.96</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
@@ -1228,12 +1228,12 @@
         <v>33</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>87.31</v>
+        <v>84.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
@@ -1242,12 +1242,12 @@
         <v>32</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>87.2</v>
+        <v>92.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
@@ -1256,7 +1256,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>84.29</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="21">

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:42</t>
+    <t xml:space="preserve">2026-09-23 16:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_coquimbo.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:25</t>
+    <t xml:space="preserve">2026-10-05 06:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
